--- a/data/output/evaluasi_52.xlsx
+++ b/data/output/evaluasi_52.xlsx
@@ -8,8 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="5200" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="5206" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="5202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="5207" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="5206" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="5202" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5203" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5205" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5208" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5271" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5201" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5272" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5204" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +481,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-8.534049914213115</v>
+        <v>-6.477287698768006</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -501,20 +509,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-9.883330483286892</v>
+        <v>-6.963324078977006</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -529,20 +537,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-20.88622436690784</v>
+        <v>-8.766384748204773</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q1-25 vs distribusi_net_ekspor_q1-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -557,20 +565,392 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-13.97399328790302</v>
+        <v>-18.36903209525278</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhk_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-9.08767702946542</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.22666473425724</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.834488126372832</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.016584672645539</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.654156613703936</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>52</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.016584672645539</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12.51427817771457</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.00604276655885</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bima</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6318485220134461</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3429862582977738</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -585,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,39 +1002,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bima</t>
+          <t>Kabupaten Sumbawa Barat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3279954.079390836</v>
+        <v>-4.719400620455216</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bima</t>
+          <t>Kabupaten Sumbawa Barat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -663,72 +1043,156 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1110740.012328828</v>
+        <v>3.919612588645375</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bima</t>
+          <t>Kabupaten Sumbawa Barat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-21.79746792426305</v>
+        <v>-3.379584669255685</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Bima</t>
+          <t>Kabupaten Sumbawa Barat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-29.09838777220078</v>
+        <v>-16.24820315748552</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3388639632138928</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.962353544424413</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumbawa Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.231887715089129</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -743,6 +1207,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.08368677363769784</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q2-25_ril vs sog_y-on-y_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bima</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.634402610966034</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9.16410635215513</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12.02017518482657</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -780,85 +1448,605 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lombok Tengah</t>
+          <t>Kabupaten Lombok Timur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.68682984080738</v>
+        <v>13.45676167083243</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pdrb_q1-25_ril vs q-to-q_pdrb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Lombok Tengah</t>
+          <t>Kabupaten Lombok Timur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.68682984080738</v>
+        <v>4.343710717244668</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pdrb_q1-25_ril vs sog_q_pdrb_q1-25_rev</t>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Lombok Tengah</t>
+          <t>Kabupaten Lombok Timur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1559575767125747</v>
+        <v>-0.1974059087194479</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.035550132495436</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Dompu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.358818364695781</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5523669902740374</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01850889388462471</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.328894496056028</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.21925644094976</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.458946515579561</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.039137444921934</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.295809924721544</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Mataram</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.567213894875437</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0356256771453656</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lombok Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2071193702275949</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_52.xlsx
+++ b/data/output/evaluasi_52.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
